--- a/content/content.xlsx
+++ b/content/content.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부서" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조직원" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="브랜드소개" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="브랜드담당" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +36,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +50,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EEF4"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,12 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -19236,20 +19246,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>부서</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>부서(한글)</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
@@ -19258,53 +19274,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>경영진</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sales Dept. 1</t>
+          <t>Sales Team 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carbon black, FMO / UV·Light Stabilizer</t>
+          <t>영업1팀</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sales Dept. 2</t>
+          <t>Sales Team 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hydrocarbon resin / PMR, Rosin</t>
+          <t>영업2팀</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sales Dept. 3</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Additives, Initiator / Functional monomer</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Administration</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+          <t>경영지원팀</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Financial, General affairs</t>
         </is>
@@ -19321,190 +19335,400 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>부서</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>이름(한글)</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>이름(영문)</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>직급</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>직급(영문)</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>담당분야</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>이메일(공개)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>정종원</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Jong Won JUNG</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>대표이사</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sales Dept. 1</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>장종진</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Jong Jin JANG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Electronics, Toners</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>부사장</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vice President</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sales Dept. 1</t>
+          <t>Sales Team 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>위재필</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Jae Pil WI</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Coatings, Inks</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>부장</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>jpwi@chemifriend.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sales Dept. 1</t>
+          <t>Sales Team 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ji Ho JEON</t>
+          <t>추교석</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Gyo Seok CHOO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>차장</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Deputy General Manager</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>gschoo@chemifriend.com</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sales Dept. 1</t>
+          <t>Sales Team 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bit Na OH</t>
+          <t>백승헌</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Seung Hun BAEK</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>shbaek@chemifriend.com</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sales Dept. 1</t>
+          <t>Sales Team 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sun Kyu LEE</t>
+          <t>오빛나</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bit Na OH</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>차장</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Deputy General Manager</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sales Dept. 2</t>
+          <t>Sales Team 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Soon Yong BAE</t>
+          <t>김유정</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Adhesives, Home care</t>
+          <t>Yu Jeong KIM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>대리</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Assistant Manager</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sales Dept. 2</t>
+          <t>Sales Team 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ju Young LEE</t>
+          <t>배순용</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Adhesives, Coatings</t>
+          <t>Soon Yong BAE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>이사</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Adhesives, Home care</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>sybae@chemifriend.com</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sales Dept. 2</t>
+          <t>Sales Team 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jeong Eun MOON</t>
+          <t>이주영</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ju Young LEE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>부장</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Adhesives, Coatings</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sales Dept. 3</t>
+          <t>Sales Team 2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jae Hoon LEE</t>
+          <t>이영욱</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Coatings, Composites</t>
+          <t>Young Wook LEE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Manager</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sales Dept. 3</t>
+          <t>Sales Team 2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>서민옥</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Min Ok SEO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -19516,12 +19740,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>서지영</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Ji Young SEO</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Financial/general affairs</t>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>부장</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Financial, General affairs</t>
         </is>
       </c>
     </row>
@@ -19710,13 +19949,143 @@
           <t>Others</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>첨가제, 안료, 용제·수지, 단량체, 글로벌 소싱, 계면활성제</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>슬러그</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>담당자(한글이름 또는 전체)</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>분야(한글)</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>분야(영문)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CABOT</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>위재필</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>코팅·잉크</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Coatings, Inks</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CABOT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>백승헌</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>플라스틱</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Plastics</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SOLVAY</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>추교석</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ARKEMA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>추교석</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SYNTHOMER-eastman</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>이영욱</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>전체</t>
         </is>
       </c>
     </row>

--- a/content/content.xlsx
+++ b/content/content.xlsx
@@ -19335,7 +19335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19632,7 +19632,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Adhesives, Home care</t>
+          <t>Henkel · Adhesives, Home care</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -19699,6 +19699,11 @@
           <t>Manager</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ywlee@chemifriend.com</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -19708,57 +19713,84 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>서민옥</t>
+          <t>문정은</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Min Ok SEO</t>
+          <t>Jeong Eun MOON</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>과장</t>
+          <t>대리</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CS</t>
+          <t>Assistant Manager</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Sales Team 2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>서민옥</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Min Ok SEO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Administration</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>서지영</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Ji Young SEO</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>부장</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Financial, General affairs</t>
         </is>
@@ -19966,7 +19998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20073,17 +20105,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>이영욱</t>
+          <t>이주영</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>SYNTHOMER-eastman</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>이영욱</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Others</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
